--- a/doc/Supplementary_2.xlsx
+++ b/doc/Supplementary_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nelly/bioinfo/Popgen_Qmacdougallii/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8966E5C-366A-1B43-9DE4-68F7E3028DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B795A9-A0AE-6249-878F-B613ED7A4E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="1140" windowWidth="38400" windowHeight="19860" activeTab="2" xr2:uid="{BA0547B8-EBFB-8C4B-B87E-DC72CEAE7662}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16260" activeTab="3" xr2:uid="{BA0547B8-EBFB-8C4B-B87E-DC72CEAE7662}"/>
   </bookViews>
   <sheets>
     <sheet name="TS1" sheetId="2" r:id="rId1"/>
@@ -1887,7 +1887,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1930,6 +1930,14 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -1986,7 +1994,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2037,6 +2045,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="11" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3656,7 +3667,12 @@
   <dimension ref="A1:W125"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="17" max="17" width="63.6640625" customWidth="1"/>
+    <col min="1" max="1" width="19.83203125" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" customWidth="1"/>
+    <col min="7" max="7" width="21.6640625" customWidth="1"/>
+    <col min="8" max="8" width="23.1640625" customWidth="1"/>
+    <col min="9" max="9" width="21.6640625" customWidth="1"/>
+    <col min="17" max="17" width="78.33203125" customWidth="1"/>
     <col min="18" max="18" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3731,74 +3747,74 @@
         <v>591</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A2" s="13" t="s">
+    <row r="2" spans="1:23" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="20" t="s">
         <v>547</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="20" t="s">
         <v>457</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="D2" s="13">
+      <c r="D2" s="20">
         <v>0.19487199999999999</v>
       </c>
-      <c r="E2" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F2" s="13">
-        <v>1</v>
-      </c>
-      <c r="G2" s="13" t="s">
+      <c r="E2" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F2" s="20">
+        <v>1</v>
+      </c>
+      <c r="G2" s="20" t="s">
         <v>457</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="20" t="s">
         <v>548</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="20" t="s">
         <v>549</v>
       </c>
-      <c r="J2" s="13">
-        <v>1</v>
-      </c>
-      <c r="K2" s="13">
-        <v>0</v>
-      </c>
-      <c r="L2" s="13">
-        <v>0</v>
-      </c>
-      <c r="M2" s="13">
-        <v>0</v>
-      </c>
-      <c r="N2" s="13">
-        <v>0</v>
-      </c>
-      <c r="O2" s="13">
-        <v>0</v>
-      </c>
-      <c r="P2" s="13">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="13" t="s">
+      <c r="J2" s="20">
+        <v>1</v>
+      </c>
+      <c r="K2" s="20">
+        <v>0</v>
+      </c>
+      <c r="L2" s="20">
+        <v>0</v>
+      </c>
+      <c r="M2" s="20">
+        <v>0</v>
+      </c>
+      <c r="N2" s="20">
+        <v>0</v>
+      </c>
+      <c r="O2" s="20">
+        <v>0</v>
+      </c>
+      <c r="P2" s="20">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="20" t="s">
         <v>550</v>
       </c>
-      <c r="R2">
+      <c r="R2" s="21">
         <v>6.0000000000000002E-112</v>
       </c>
-      <c r="S2" s="13">
+      <c r="S2" s="20">
         <v>0.99</v>
       </c>
-      <c r="T2" s="13" t="s">
+      <c r="T2" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="U2" s="13" t="s">
+      <c r="U2" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="V2" s="13" t="s">
+      <c r="V2" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="W2" s="13" t="s">
+      <c r="W2" s="20" t="s">
         <v>593</v>
       </c>
     </row>
@@ -3944,74 +3960,74 @@
         <v>592</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:23" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="20" t="s">
         <v>573</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="20" t="s">
         <v>457</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="20">
         <v>0.27649800000000002</v>
       </c>
-      <c r="E5" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F5" s="13">
-        <v>1</v>
-      </c>
-      <c r="G5" s="13" t="s">
+      <c r="E5" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F5" s="20">
+        <v>1</v>
+      </c>
+      <c r="G5" s="20" t="s">
         <v>457</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="20" t="s">
         <v>574</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="20" t="s">
         <v>575</v>
       </c>
-      <c r="J5" s="13">
-        <v>0</v>
-      </c>
-      <c r="K5" s="13">
-        <v>1</v>
-      </c>
-      <c r="L5" s="13">
-        <v>0</v>
-      </c>
-      <c r="M5" s="13">
-        <v>0</v>
-      </c>
-      <c r="N5" s="13">
-        <v>1</v>
-      </c>
-      <c r="O5" s="13">
-        <v>0</v>
-      </c>
-      <c r="P5" s="13">
+      <c r="J5" s="20">
+        <v>0</v>
+      </c>
+      <c r="K5" s="20">
+        <v>1</v>
+      </c>
+      <c r="L5" s="20">
+        <v>0</v>
+      </c>
+      <c r="M5" s="20">
+        <v>0</v>
+      </c>
+      <c r="N5" s="20">
+        <v>1</v>
+      </c>
+      <c r="O5" s="20">
+        <v>0</v>
+      </c>
+      <c r="P5" s="20">
         <v>2</v>
       </c>
-      <c r="Q5" s="13" t="s">
+      <c r="Q5" s="20" t="s">
         <v>475</v>
       </c>
-      <c r="R5" s="19">
+      <c r="R5" s="22">
         <v>7.9999999999999996E-6</v>
       </c>
-      <c r="S5" s="13">
+      <c r="S5" s="20">
         <v>0.87</v>
       </c>
-      <c r="T5" s="13" t="s">
+      <c r="T5" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="U5" s="13" t="s">
+      <c r="U5" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="V5" s="13" t="s">
+      <c r="V5" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="W5" s="13" t="s">
+      <c r="W5" s="20" t="s">
         <v>593</v>
       </c>
     </row>
@@ -4370,74 +4386,74 @@
         <v>592</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A11" s="13" t="s">
+    <row r="11" spans="1:23" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="20" t="s">
         <v>505</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="20" t="s">
         <v>457</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="20">
         <v>0.19487199999999999</v>
       </c>
-      <c r="E11" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F11" s="13">
-        <v>1</v>
-      </c>
-      <c r="G11" s="13" t="s">
+      <c r="E11" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F11" s="20">
+        <v>1</v>
+      </c>
+      <c r="G11" s="20" t="s">
         <v>457</v>
       </c>
-      <c r="H11" s="13" t="s">
+      <c r="H11" s="20" t="s">
         <v>506</v>
       </c>
-      <c r="I11" s="13" t="s">
+      <c r="I11" s="20" t="s">
         <v>507</v>
       </c>
-      <c r="J11" s="13">
-        <v>0</v>
-      </c>
-      <c r="K11" s="13">
-        <v>0</v>
-      </c>
-      <c r="L11" s="13">
-        <v>0</v>
-      </c>
-      <c r="M11" s="13">
-        <v>0</v>
-      </c>
-      <c r="N11" s="13">
-        <v>0</v>
-      </c>
-      <c r="O11" s="13">
-        <v>0</v>
-      </c>
-      <c r="P11" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="13" t="s">
+      <c r="J11" s="20">
+        <v>0</v>
+      </c>
+      <c r="K11" s="20">
+        <v>0</v>
+      </c>
+      <c r="L11" s="20">
+        <v>0</v>
+      </c>
+      <c r="M11" s="20">
+        <v>0</v>
+      </c>
+      <c r="N11" s="20">
+        <v>0</v>
+      </c>
+      <c r="O11" s="20">
+        <v>0</v>
+      </c>
+      <c r="P11" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="20" t="s">
         <v>508</v>
       </c>
-      <c r="R11">
+      <c r="R11" s="21">
         <v>6.0000000000000006E-20</v>
       </c>
-      <c r="S11" s="13">
+      <c r="S11" s="20">
         <v>0.8</v>
       </c>
-      <c r="T11" s="13" t="s">
+      <c r="T11" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="U11" s="13" t="s">
+      <c r="U11" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="V11" s="13" t="s">
+      <c r="V11" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="W11" s="13" t="s">
+      <c r="W11" s="20" t="s">
         <v>593</v>
       </c>
     </row>
@@ -4725,216 +4741,216 @@
         <v>592</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A16" s="13" t="s">
+    <row r="16" spans="1:23" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="20" t="s">
         <v>542</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="20" t="s">
         <v>457</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="D16" s="13">
+      <c r="D16" s="20">
         <v>0.19487199999999999</v>
       </c>
-      <c r="E16" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F16" s="13">
-        <v>1</v>
-      </c>
-      <c r="G16" s="13" t="s">
+      <c r="E16" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" s="20">
+        <v>1</v>
+      </c>
+      <c r="G16" s="20" t="s">
         <v>457</v>
       </c>
-      <c r="H16" s="13" t="s">
+      <c r="H16" s="20" t="s">
         <v>543</v>
       </c>
-      <c r="I16" s="13" t="s">
+      <c r="I16" s="20" t="s">
         <v>544</v>
       </c>
-      <c r="J16" s="13">
+      <c r="J16" s="20">
         <v>2</v>
       </c>
-      <c r="K16" s="13">
-        <v>1</v>
-      </c>
-      <c r="L16" s="13">
-        <v>0</v>
-      </c>
-      <c r="M16" s="13">
-        <v>0</v>
-      </c>
-      <c r="N16" s="13">
-        <v>0</v>
-      </c>
-      <c r="O16" s="13">
+      <c r="K16" s="20">
+        <v>1</v>
+      </c>
+      <c r="L16" s="20">
+        <v>0</v>
+      </c>
+      <c r="M16" s="20">
+        <v>0</v>
+      </c>
+      <c r="N16" s="20">
+        <v>0</v>
+      </c>
+      <c r="O16" s="20">
         <v>2</v>
       </c>
-      <c r="P16" s="13">
+      <c r="P16" s="20">
         <v>5</v>
       </c>
-      <c r="Q16" s="13" t="s">
+      <c r="Q16" s="20" t="s">
         <v>545</v>
       </c>
-      <c r="R16">
+      <c r="R16" s="21">
         <v>4.9999999999999997E-30</v>
       </c>
-      <c r="S16" s="13">
+      <c r="S16" s="20">
         <v>0.89</v>
       </c>
-      <c r="T16" s="13" t="s">
+      <c r="T16" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="U16" s="13" t="s">
+      <c r="U16" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="V16" s="13" t="s">
+      <c r="V16" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="W16" s="13" t="s">
+      <c r="W16" s="20" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A17" s="13" t="s">
+    <row r="17" spans="1:23" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="20" t="s">
         <v>378</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="20" t="s">
         <v>359</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="D17" s="13">
+      <c r="D17" s="20">
         <v>0.110995</v>
       </c>
-      <c r="E17" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F17" s="13">
-        <v>1</v>
-      </c>
-      <c r="G17" s="13" t="s">
+      <c r="E17" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" s="20">
+        <v>1</v>
+      </c>
+      <c r="G17" s="20" t="s">
         <v>359</v>
       </c>
-      <c r="H17" s="13" t="s">
+      <c r="H17" s="20" t="s">
         <v>379</v>
       </c>
-      <c r="I17" s="13" t="s">
+      <c r="I17" s="20" t="s">
         <v>380</v>
       </c>
-      <c r="J17" s="13">
-        <v>0</v>
-      </c>
-      <c r="K17" s="13">
-        <v>0</v>
-      </c>
-      <c r="L17" s="13">
-        <v>1</v>
-      </c>
-      <c r="M17" s="13">
-        <v>0</v>
-      </c>
-      <c r="N17" s="13">
-        <v>0</v>
-      </c>
-      <c r="O17" s="13">
-        <v>0</v>
-      </c>
-      <c r="P17" s="13">
-        <v>1</v>
-      </c>
-      <c r="Q17" s="13" t="s">
+      <c r="J17" s="20">
+        <v>0</v>
+      </c>
+      <c r="K17" s="20">
+        <v>0</v>
+      </c>
+      <c r="L17" s="20">
+        <v>1</v>
+      </c>
+      <c r="M17" s="20">
+        <v>0</v>
+      </c>
+      <c r="N17" s="20">
+        <v>0</v>
+      </c>
+      <c r="O17" s="20">
+        <v>0</v>
+      </c>
+      <c r="P17" s="20">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="20" t="s">
         <v>381</v>
       </c>
-      <c r="R17">
+      <c r="R17" s="21">
         <v>8.0000000000000007E-31</v>
       </c>
-      <c r="S17" s="13">
+      <c r="S17" s="20">
         <v>0.9</v>
       </c>
-      <c r="T17" s="13" t="s">
+      <c r="T17" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="U17" s="13" t="s">
+      <c r="U17" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="V17" s="13" t="s">
+      <c r="V17" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="W17" s="13" t="s">
+      <c r="W17" s="20" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A18" s="13" t="s">
+    <row r="18" spans="1:23" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="D18" s="13">
+      <c r="D18" s="20">
         <v>1.57E-6</v>
       </c>
-      <c r="E18" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F18" s="13">
+      <c r="E18" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F18" s="20">
         <v>4</v>
       </c>
-      <c r="G18" s="13" t="s">
+      <c r="G18" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="H18" s="13" t="s">
+      <c r="H18" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="I18" s="13" t="s">
+      <c r="I18" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="J18" s="13">
-        <v>0</v>
-      </c>
-      <c r="K18" s="13">
-        <v>0</v>
-      </c>
-      <c r="L18" s="13">
-        <v>0</v>
-      </c>
-      <c r="M18" s="13">
-        <v>0</v>
-      </c>
-      <c r="N18" s="13">
-        <v>0</v>
-      </c>
-      <c r="O18" s="13">
-        <v>0</v>
-      </c>
-      <c r="P18" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="13" t="s">
+      <c r="J18" s="20">
+        <v>0</v>
+      </c>
+      <c r="K18" s="20">
+        <v>0</v>
+      </c>
+      <c r="L18" s="20">
+        <v>0</v>
+      </c>
+      <c r="M18" s="20">
+        <v>0</v>
+      </c>
+      <c r="N18" s="20">
+        <v>0</v>
+      </c>
+      <c r="O18" s="20">
+        <v>0</v>
+      </c>
+      <c r="P18" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="R18">
+      <c r="R18" s="21">
         <v>9.0000000000000004E-62</v>
       </c>
-      <c r="S18" s="13">
+      <c r="S18" s="20">
         <v>0.99</v>
       </c>
-      <c r="T18" s="13" t="s">
+      <c r="T18" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="U18" s="13" t="s">
+      <c r="U18" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="V18" s="13" t="s">
+      <c r="V18" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="W18" s="13" t="s">
+      <c r="W18" s="20" t="s">
         <v>593</v>
       </c>
     </row>
@@ -6216,145 +6232,145 @@
         <v>592</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A37" s="13" t="s">
+    <row r="37" spans="1:23" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="20" t="s">
         <v>222</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="D37" s="13">
+      <c r="D37" s="20">
         <v>0.14888299999999999</v>
       </c>
-      <c r="E37" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F37" s="13">
+      <c r="E37" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F37" s="20">
         <v>2</v>
       </c>
-      <c r="G37" s="13" t="s">
+      <c r="G37" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="H37" s="13" t="s">
+      <c r="H37" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="I37" s="13" t="s">
+      <c r="I37" s="20" t="s">
         <v>224</v>
       </c>
-      <c r="J37" s="13">
-        <v>0</v>
-      </c>
-      <c r="K37" s="13">
-        <v>0</v>
-      </c>
-      <c r="L37" s="13">
-        <v>0</v>
-      </c>
-      <c r="M37" s="13">
-        <v>0</v>
-      </c>
-      <c r="N37" s="13">
-        <v>0</v>
-      </c>
-      <c r="O37" s="13">
-        <v>0</v>
-      </c>
-      <c r="P37" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="13" t="s">
+      <c r="J37" s="20">
+        <v>0</v>
+      </c>
+      <c r="K37" s="20">
+        <v>0</v>
+      </c>
+      <c r="L37" s="20">
+        <v>0</v>
+      </c>
+      <c r="M37" s="20">
+        <v>0</v>
+      </c>
+      <c r="N37" s="20">
+        <v>0</v>
+      </c>
+      <c r="O37" s="20">
+        <v>0</v>
+      </c>
+      <c r="P37" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="R37">
+      <c r="R37" s="21">
         <v>9.9999999999999997E-61</v>
       </c>
-      <c r="S37" s="13">
+      <c r="S37" s="20">
         <v>0.99</v>
       </c>
-      <c r="T37" s="13" t="s">
+      <c r="T37" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="U37" s="13" t="s">
+      <c r="U37" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="V37" s="13" t="s">
+      <c r="V37" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="W37" s="13" t="s">
+      <c r="W37" s="20" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A38" s="13" t="s">
+    <row r="38" spans="1:23" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="20" t="s">
         <v>227</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C38" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="D38" s="13">
+      <c r="D38" s="20">
         <v>0.14888299999999999</v>
       </c>
-      <c r="E38" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F38" s="13">
+      <c r="E38" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F38" s="20">
         <v>2</v>
       </c>
-      <c r="G38" s="13" t="s">
+      <c r="G38" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="H38" s="13" t="s">
+      <c r="H38" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="I38" s="13" t="s">
+      <c r="I38" s="20" t="s">
         <v>224</v>
       </c>
-      <c r="J38" s="13">
-        <v>0</v>
-      </c>
-      <c r="K38" s="13">
-        <v>0</v>
-      </c>
-      <c r="L38" s="13">
-        <v>0</v>
-      </c>
-      <c r="M38" s="13">
-        <v>0</v>
-      </c>
-      <c r="N38" s="13">
-        <v>0</v>
-      </c>
-      <c r="O38" s="13">
-        <v>0</v>
-      </c>
-      <c r="P38" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="13" t="s">
+      <c r="J38" s="20">
+        <v>0</v>
+      </c>
+      <c r="K38" s="20">
+        <v>0</v>
+      </c>
+      <c r="L38" s="20">
+        <v>0</v>
+      </c>
+      <c r="M38" s="20">
+        <v>0</v>
+      </c>
+      <c r="N38" s="20">
+        <v>0</v>
+      </c>
+      <c r="O38" s="20">
+        <v>0</v>
+      </c>
+      <c r="P38" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="R38">
+      <c r="R38" s="21">
         <v>9.9999999999999997E-61</v>
       </c>
-      <c r="S38" s="13">
+      <c r="S38" s="20">
         <v>0.99</v>
       </c>
-      <c r="T38" s="13" t="s">
+      <c r="T38" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="U38" s="13" t="s">
+      <c r="U38" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="V38" s="13" t="s">
+      <c r="V38" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="W38" s="13" t="s">
+      <c r="W38" s="20" t="s">
         <v>593</v>
       </c>
     </row>
@@ -6500,74 +6516,74 @@
         <v>592</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A41" s="13" t="s">
+    <row r="41" spans="1:23" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="20" t="s">
         <v>374</v>
       </c>
-      <c r="B41" s="13" t="s">
+      <c r="B41" s="20" t="s">
         <v>359</v>
       </c>
-      <c r="C41" s="13" t="s">
+      <c r="C41" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="D41" s="13">
+      <c r="D41" s="20">
         <v>8.5278000000000007E-2</v>
       </c>
-      <c r="E41" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F41" s="13">
-        <v>1</v>
-      </c>
-      <c r="G41" s="13" t="s">
+      <c r="E41" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F41" s="20">
+        <v>1</v>
+      </c>
+      <c r="G41" s="20" t="s">
         <v>359</v>
       </c>
-      <c r="H41" s="13" t="s">
+      <c r="H41" s="20" t="s">
         <v>375</v>
       </c>
-      <c r="I41" s="13" t="s">
+      <c r="I41" s="20" t="s">
         <v>376</v>
       </c>
-      <c r="J41" s="13">
-        <v>1</v>
-      </c>
-      <c r="K41" s="13">
-        <v>0</v>
-      </c>
-      <c r="L41" s="13">
-        <v>1</v>
-      </c>
-      <c r="M41" s="13">
-        <v>0</v>
-      </c>
-      <c r="N41" s="13">
-        <v>1</v>
-      </c>
-      <c r="O41" s="13">
-        <v>0</v>
-      </c>
-      <c r="P41" s="13">
+      <c r="J41" s="20">
+        <v>1</v>
+      </c>
+      <c r="K41" s="20">
+        <v>0</v>
+      </c>
+      <c r="L41" s="20">
+        <v>1</v>
+      </c>
+      <c r="M41" s="20">
+        <v>0</v>
+      </c>
+      <c r="N41" s="20">
+        <v>1</v>
+      </c>
+      <c r="O41" s="20">
+        <v>0</v>
+      </c>
+      <c r="P41" s="20">
         <v>3</v>
       </c>
-      <c r="Q41" s="13" t="s">
+      <c r="Q41" s="20" t="s">
         <v>377</v>
       </c>
-      <c r="R41">
+      <c r="R41" s="21">
         <v>1E-27</v>
       </c>
-      <c r="S41" s="13">
+      <c r="S41" s="20">
         <v>0.99</v>
       </c>
-      <c r="T41" s="13" t="s">
+      <c r="T41" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="U41" s="13" t="s">
+      <c r="U41" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="V41" s="13" t="s">
+      <c r="V41" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="W41" s="13" t="s">
+      <c r="W41" s="20" t="s">
         <v>593</v>
       </c>
     </row>
@@ -6784,74 +6800,74 @@
         <v>592</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A45" s="13" t="s">
+    <row r="45" spans="1:23" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="20" t="s">
         <v>472</v>
       </c>
-      <c r="B45" s="13" t="s">
+      <c r="B45" s="20" t="s">
         <v>457</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="C45" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="D45" s="13">
+      <c r="D45" s="20">
         <v>0.179314</v>
       </c>
-      <c r="E45" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F45" s="13">
-        <v>1</v>
-      </c>
-      <c r="G45" s="13" t="s">
+      <c r="E45" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F45" s="20">
+        <v>1</v>
+      </c>
+      <c r="G45" s="20" t="s">
         <v>457</v>
       </c>
-      <c r="H45" s="13" t="s">
+      <c r="H45" s="20" t="s">
         <v>473</v>
       </c>
-      <c r="I45" s="13" t="s">
+      <c r="I45" s="20" t="s">
         <v>474</v>
       </c>
-      <c r="J45" s="13">
-        <v>0</v>
-      </c>
-      <c r="K45" s="13">
-        <v>0</v>
-      </c>
-      <c r="L45" s="13">
-        <v>0</v>
-      </c>
-      <c r="M45" s="13">
-        <v>0</v>
-      </c>
-      <c r="N45" s="13">
-        <v>0</v>
-      </c>
-      <c r="O45" s="13">
-        <v>0</v>
-      </c>
-      <c r="P45" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="13" t="s">
+      <c r="J45" s="20">
+        <v>0</v>
+      </c>
+      <c r="K45" s="20">
+        <v>0</v>
+      </c>
+      <c r="L45" s="20">
+        <v>0</v>
+      </c>
+      <c r="M45" s="20">
+        <v>0</v>
+      </c>
+      <c r="N45" s="20">
+        <v>0</v>
+      </c>
+      <c r="O45" s="20">
+        <v>0</v>
+      </c>
+      <c r="P45" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="20" t="s">
         <v>475</v>
       </c>
-      <c r="R45" s="19">
+      <c r="R45" s="22">
         <v>4.0000000000000002E-9</v>
       </c>
-      <c r="S45" s="13">
+      <c r="S45" s="20">
         <v>0.84</v>
       </c>
-      <c r="T45" s="13" t="s">
+      <c r="T45" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="U45" s="13" t="s">
+      <c r="U45" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="V45" s="13" t="s">
+      <c r="V45" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="W45" s="13" t="s">
+      <c r="W45" s="20" t="s">
         <v>593</v>
       </c>
     </row>
@@ -7281,74 +7297,74 @@
         <v>592</v>
       </c>
     </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A52" s="13" t="s">
+    <row r="52" spans="1:23" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="20" t="s">
         <v>463</v>
       </c>
-      <c r="B52" s="13" t="s">
+      <c r="B52" s="20" t="s">
         <v>457</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="C52" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="D52" s="13">
+      <c r="D52" s="20">
         <v>0.18865399999999999</v>
       </c>
-      <c r="E52" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F52" s="13">
-        <v>1</v>
-      </c>
-      <c r="G52" s="13" t="s">
+      <c r="E52" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F52" s="20">
+        <v>1</v>
+      </c>
+      <c r="G52" s="20" t="s">
         <v>457</v>
       </c>
-      <c r="H52" s="13" t="s">
+      <c r="H52" s="20" t="s">
         <v>464</v>
       </c>
-      <c r="I52" s="13" t="s">
+      <c r="I52" s="20" t="s">
         <v>465</v>
       </c>
-      <c r="J52" s="13">
-        <v>0</v>
-      </c>
-      <c r="K52" s="13">
-        <v>0</v>
-      </c>
-      <c r="L52" s="13">
-        <v>0</v>
-      </c>
-      <c r="M52" s="13">
-        <v>0</v>
-      </c>
-      <c r="N52" s="13">
-        <v>0</v>
-      </c>
-      <c r="O52" s="13">
-        <v>0</v>
-      </c>
-      <c r="P52" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="13" t="s">
+      <c r="J52" s="20">
+        <v>0</v>
+      </c>
+      <c r="K52" s="20">
+        <v>0</v>
+      </c>
+      <c r="L52" s="20">
+        <v>0</v>
+      </c>
+      <c r="M52" s="20">
+        <v>0</v>
+      </c>
+      <c r="N52" s="20">
+        <v>0</v>
+      </c>
+      <c r="O52" s="20">
+        <v>0</v>
+      </c>
+      <c r="P52" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="20" t="s">
         <v>466</v>
       </c>
-      <c r="R52">
+      <c r="R52" s="21">
         <v>6.9999999999999996E-56</v>
       </c>
-      <c r="S52" s="13">
-        <v>1</v>
-      </c>
-      <c r="T52" s="13" t="s">
+      <c r="S52" s="20">
+        <v>1</v>
+      </c>
+      <c r="T52" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="U52" s="13" t="s">
+      <c r="U52" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="V52" s="13" t="s">
+      <c r="V52" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="W52" s="13" t="s">
+      <c r="W52" s="20" t="s">
         <v>593</v>
       </c>
     </row>
@@ -7423,74 +7439,74 @@
         <v>592</v>
       </c>
     </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A54" s="13" t="s">
+    <row r="54" spans="1:23" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="20" t="s">
         <v>482</v>
       </c>
-      <c r="B54" s="13" t="s">
+      <c r="B54" s="20" t="s">
         <v>457</v>
       </c>
-      <c r="C54" s="13" t="s">
+      <c r="C54" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="D54" s="13">
+      <c r="D54" s="20">
         <v>0.27649800000000002</v>
       </c>
-      <c r="E54" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F54" s="13">
-        <v>1</v>
-      </c>
-      <c r="G54" s="13" t="s">
+      <c r="E54" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F54" s="20">
+        <v>1</v>
+      </c>
+      <c r="G54" s="20" t="s">
         <v>457</v>
       </c>
-      <c r="H54" s="13" t="s">
+      <c r="H54" s="20" t="s">
         <v>483</v>
       </c>
-      <c r="I54" s="13" t="s">
+      <c r="I54" s="20" t="s">
         <v>484</v>
       </c>
-      <c r="J54" s="13">
-        <v>0</v>
-      </c>
-      <c r="K54" s="13">
-        <v>0</v>
-      </c>
-      <c r="L54" s="13">
-        <v>0</v>
-      </c>
-      <c r="M54" s="13">
-        <v>0</v>
-      </c>
-      <c r="N54" s="13">
-        <v>0</v>
-      </c>
-      <c r="O54" s="13">
-        <v>0</v>
-      </c>
-      <c r="P54" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="13" t="s">
+      <c r="J54" s="20">
+        <v>0</v>
+      </c>
+      <c r="K54" s="20">
+        <v>0</v>
+      </c>
+      <c r="L54" s="20">
+        <v>0</v>
+      </c>
+      <c r="M54" s="20">
+        <v>0</v>
+      </c>
+      <c r="N54" s="20">
+        <v>0</v>
+      </c>
+      <c r="O54" s="20">
+        <v>0</v>
+      </c>
+      <c r="P54" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="20" t="s">
         <v>485</v>
       </c>
-      <c r="R54">
+      <c r="R54" s="21">
         <v>3.0000000000000001E-62</v>
       </c>
-      <c r="S54" s="13">
+      <c r="S54" s="20">
         <v>0.99</v>
       </c>
-      <c r="T54" s="13" t="s">
+      <c r="T54" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="U54" s="13" t="s">
+      <c r="U54" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="V54" s="13" t="s">
+      <c r="V54" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="W54" s="13" t="s">
+      <c r="W54" s="20" t="s">
         <v>593</v>
       </c>
     </row>
@@ -9553,74 +9569,74 @@
         <v>592</v>
       </c>
     </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A84" s="13" t="s">
+    <row r="84" spans="1:23" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="B84" s="13" t="s">
+      <c r="B84" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="C84" s="13" t="s">
+      <c r="C84" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="D84" s="13">
+      <c r="D84" s="20">
         <v>0.11948599999999999</v>
       </c>
-      <c r="E84" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F84" s="13">
+      <c r="E84" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F84" s="20">
         <v>2</v>
       </c>
-      <c r="G84" s="13" t="s">
+      <c r="G84" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="H84" s="13" t="s">
+      <c r="H84" s="20" t="s">
         <v>218</v>
       </c>
-      <c r="I84" s="13" t="s">
+      <c r="I84" s="20" t="s">
         <v>219</v>
       </c>
-      <c r="J84" s="13">
-        <v>0</v>
-      </c>
-      <c r="K84" s="13">
-        <v>0</v>
-      </c>
-      <c r="L84" s="13">
-        <v>0</v>
-      </c>
-      <c r="M84" s="13">
-        <v>0</v>
-      </c>
-      <c r="N84" s="13">
-        <v>0</v>
-      </c>
-      <c r="O84" s="13">
-        <v>0</v>
-      </c>
-      <c r="P84" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q84" s="13" t="s">
+      <c r="J84" s="20">
+        <v>0</v>
+      </c>
+      <c r="K84" s="20">
+        <v>0</v>
+      </c>
+      <c r="L84" s="20">
+        <v>0</v>
+      </c>
+      <c r="M84" s="20">
+        <v>0</v>
+      </c>
+      <c r="N84" s="20">
+        <v>0</v>
+      </c>
+      <c r="O84" s="20">
+        <v>0</v>
+      </c>
+      <c r="P84" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="20" t="s">
         <v>220</v>
       </c>
-      <c r="R84">
+      <c r="R84" s="21">
         <v>4.9999999999999996E-40</v>
       </c>
-      <c r="S84" s="13">
-        <v>1</v>
-      </c>
-      <c r="T84" s="13" t="s">
+      <c r="S84" s="20">
+        <v>1</v>
+      </c>
+      <c r="T84" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="U84" s="13" t="s">
+      <c r="U84" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="V84" s="13" t="s">
+      <c r="V84" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="W84" s="13" t="s">
+      <c r="W84" s="20" t="s">
         <v>593</v>
       </c>
     </row>
@@ -9837,74 +9853,74 @@
         <v>592</v>
       </c>
     </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A88" s="13" t="s">
+    <row r="88" spans="1:23" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="B88" s="13" t="s">
+      <c r="B88" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="C88" s="13" t="s">
+      <c r="C88" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="D88" s="13">
+      <c r="D88" s="20">
         <v>1.8700000000000001E-5</v>
       </c>
-      <c r="E88" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F88" s="13">
+      <c r="E88" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F88" s="20">
         <v>3</v>
       </c>
-      <c r="G88" s="13" t="s">
+      <c r="G88" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="H88" s="13" t="s">
+      <c r="H88" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="I88" s="13" t="s">
+      <c r="I88" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="J88" s="13">
-        <v>0</v>
-      </c>
-      <c r="K88" s="13">
-        <v>0</v>
-      </c>
-      <c r="L88" s="13">
-        <v>0</v>
-      </c>
-      <c r="M88" s="13">
-        <v>0</v>
-      </c>
-      <c r="N88" s="13">
-        <v>0</v>
-      </c>
-      <c r="O88" s="13">
-        <v>0</v>
-      </c>
-      <c r="P88" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q88" s="13" t="s">
+      <c r="J88" s="20">
+        <v>0</v>
+      </c>
+      <c r="K88" s="20">
+        <v>0</v>
+      </c>
+      <c r="L88" s="20">
+        <v>0</v>
+      </c>
+      <c r="M88" s="20">
+        <v>0</v>
+      </c>
+      <c r="N88" s="20">
+        <v>0</v>
+      </c>
+      <c r="O88" s="20">
+        <v>0</v>
+      </c>
+      <c r="P88" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="R88">
+      <c r="R88" s="21">
         <v>1E-27</v>
       </c>
-      <c r="S88" s="13">
+      <c r="S88" s="20">
         <v>0.99</v>
       </c>
-      <c r="T88" s="13" t="s">
+      <c r="T88" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="U88" s="13" t="s">
+      <c r="U88" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="V88" s="13" t="s">
+      <c r="V88" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="W88" s="13" t="s">
+      <c r="W88" s="20" t="s">
         <v>593</v>
       </c>
     </row>
@@ -11470,74 +11486,74 @@
         <v>592</v>
       </c>
     </row>
-    <row r="111" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A111" s="13" t="s">
+    <row r="111" spans="1:23" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="20" t="s">
         <v>331</v>
       </c>
-      <c r="B111" s="13" t="s">
+      <c r="B111" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="C111" s="13" t="s">
+      <c r="C111" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="D111" s="13">
+      <c r="D111" s="20">
         <v>0.101955</v>
       </c>
-      <c r="E111" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F111" s="13">
-        <v>1</v>
-      </c>
-      <c r="G111" s="13" t="s">
+      <c r="E111" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F111" s="20">
+        <v>1</v>
+      </c>
+      <c r="G111" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="H111" s="13" t="s">
+      <c r="H111" s="20" t="s">
         <v>332</v>
       </c>
-      <c r="I111" s="13" t="s">
+      <c r="I111" s="20" t="s">
         <v>333</v>
       </c>
-      <c r="J111" s="13">
-        <v>1</v>
-      </c>
-      <c r="K111" s="13">
-        <v>0</v>
-      </c>
-      <c r="L111" s="13">
-        <v>1</v>
-      </c>
-      <c r="M111" s="13">
-        <v>0</v>
-      </c>
-      <c r="N111" s="13">
-        <v>0</v>
-      </c>
-      <c r="O111" s="13">
-        <v>0</v>
-      </c>
-      <c r="P111" s="13">
+      <c r="J111" s="20">
+        <v>1</v>
+      </c>
+      <c r="K111" s="20">
+        <v>0</v>
+      </c>
+      <c r="L111" s="20">
+        <v>1</v>
+      </c>
+      <c r="M111" s="20">
+        <v>0</v>
+      </c>
+      <c r="N111" s="20">
+        <v>0</v>
+      </c>
+      <c r="O111" s="20">
+        <v>0</v>
+      </c>
+      <c r="P111" s="20">
         <v>2</v>
       </c>
-      <c r="Q111" s="13" t="s">
+      <c r="Q111" s="20" t="s">
         <v>334</v>
       </c>
-      <c r="R111">
+      <c r="R111" s="21">
         <v>2.0000000000000001E-13</v>
       </c>
-      <c r="S111" s="13">
-        <v>1</v>
-      </c>
-      <c r="T111" s="13" t="s">
+      <c r="S111" s="20">
+        <v>1</v>
+      </c>
+      <c r="T111" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="U111" s="13" t="s">
+      <c r="U111" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="V111" s="13" t="s">
+      <c r="V111" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="W111" s="13" t="s">
+      <c r="W111" s="20" t="s">
         <v>593</v>
       </c>
     </row>
@@ -11612,74 +11628,74 @@
         <v>592</v>
       </c>
     </row>
-    <row r="113" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A113" s="13" t="s">
+    <row r="113" spans="1:23" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="20" t="s">
         <v>477</v>
       </c>
-      <c r="B113" s="13" t="s">
+      <c r="B113" s="20" t="s">
         <v>457</v>
       </c>
-      <c r="C113" s="13" t="s">
+      <c r="C113" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="D113" s="13">
+      <c r="D113" s="20">
         <v>0.19164800000000001</v>
       </c>
-      <c r="E113" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F113" s="13">
-        <v>1</v>
-      </c>
-      <c r="G113" s="13" t="s">
+      <c r="E113" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F113" s="20">
+        <v>1</v>
+      </c>
+      <c r="G113" s="20" t="s">
         <v>457</v>
       </c>
-      <c r="H113" s="13" t="s">
+      <c r="H113" s="20" t="s">
         <v>478</v>
       </c>
-      <c r="I113" s="13" t="s">
+      <c r="I113" s="20" t="s">
         <v>479</v>
       </c>
-      <c r="J113" s="13">
-        <v>0</v>
-      </c>
-      <c r="K113" s="13">
-        <v>0</v>
-      </c>
-      <c r="L113" s="13">
-        <v>0</v>
-      </c>
-      <c r="M113" s="13">
-        <v>0</v>
-      </c>
-      <c r="N113" s="13">
-        <v>0</v>
-      </c>
-      <c r="O113" s="13">
-        <v>0</v>
-      </c>
-      <c r="P113" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q113" s="13" t="s">
+      <c r="J113" s="20">
+        <v>0</v>
+      </c>
+      <c r="K113" s="20">
+        <v>0</v>
+      </c>
+      <c r="L113" s="20">
+        <v>0</v>
+      </c>
+      <c r="M113" s="20">
+        <v>0</v>
+      </c>
+      <c r="N113" s="20">
+        <v>0</v>
+      </c>
+      <c r="O113" s="20">
+        <v>0</v>
+      </c>
+      <c r="P113" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q113" s="20" t="s">
         <v>480</v>
       </c>
-      <c r="R113">
+      <c r="R113" s="21">
         <v>1.9999999999999999E-60</v>
       </c>
-      <c r="S113" s="13">
+      <c r="S113" s="20">
         <v>0.97</v>
       </c>
-      <c r="T113" s="13" t="s">
+      <c r="T113" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="U113" s="13" t="s">
+      <c r="U113" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="V113" s="13" t="s">
+      <c r="V113" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="W113" s="13" t="s">
+      <c r="W113" s="20" t="s">
         <v>593</v>
       </c>
     </row>
@@ -11825,74 +11841,74 @@
         <v>592</v>
       </c>
     </row>
-    <row r="116" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A116" s="13" t="s">
+    <row r="116" spans="1:23" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="B116" s="13" t="s">
+      <c r="B116" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="C116" s="13" t="s">
+      <c r="C116" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="D116" s="13">
+      <c r="D116" s="20">
         <v>0.148731</v>
       </c>
-      <c r="E116" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F116" s="13">
+      <c r="E116" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F116" s="20">
         <v>3</v>
       </c>
-      <c r="G116" s="13" t="s">
+      <c r="G116" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="H116" s="13" t="s">
+      <c r="H116" s="20" t="s">
         <v>241</v>
       </c>
-      <c r="I116" s="13" t="s">
+      <c r="I116" s="20" t="s">
         <v>242</v>
       </c>
-      <c r="J116" s="13">
-        <v>1</v>
-      </c>
-      <c r="K116" s="13">
-        <v>0</v>
-      </c>
-      <c r="L116" s="13">
-        <v>0</v>
-      </c>
-      <c r="M116" s="13">
-        <v>1</v>
-      </c>
-      <c r="N116" s="13">
-        <v>0</v>
-      </c>
-      <c r="O116" s="13">
-        <v>0</v>
-      </c>
-      <c r="P116" s="13">
+      <c r="J116" s="20">
+        <v>1</v>
+      </c>
+      <c r="K116" s="20">
+        <v>0</v>
+      </c>
+      <c r="L116" s="20">
+        <v>0</v>
+      </c>
+      <c r="M116" s="20">
+        <v>1</v>
+      </c>
+      <c r="N116" s="20">
+        <v>0</v>
+      </c>
+      <c r="O116" s="20">
+        <v>0</v>
+      </c>
+      <c r="P116" s="20">
         <v>2</v>
       </c>
-      <c r="Q116" s="13" t="s">
+      <c r="Q116" s="20" t="s">
         <v>243</v>
       </c>
-      <c r="R116">
+      <c r="R116" s="21">
         <v>1.9999999999999999E-57</v>
       </c>
-      <c r="S116" s="13">
+      <c r="S116" s="20">
         <v>0.98</v>
       </c>
-      <c r="T116" s="13" t="s">
+      <c r="T116" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="U116" s="13" t="s">
+      <c r="U116" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="V116" s="13" t="s">
+      <c r="V116" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="W116" s="13" t="s">
+      <c r="W116" s="20" t="s">
         <v>593</v>
       </c>
     </row>
@@ -12038,74 +12054,74 @@
         <v>592</v>
       </c>
     </row>
-    <row r="119" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A119" s="13" t="s">
+    <row r="119" spans="1:23" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A119" s="20" t="s">
         <v>525</v>
       </c>
-      <c r="B119" s="13" t="s">
+      <c r="B119" s="20" t="s">
         <v>457</v>
       </c>
-      <c r="C119" s="13" t="s">
+      <c r="C119" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="D119" s="13">
+      <c r="D119" s="20">
         <v>0.19897999999999999</v>
       </c>
-      <c r="E119" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F119" s="13">
-        <v>1</v>
-      </c>
-      <c r="G119" s="13" t="s">
+      <c r="E119" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F119" s="20">
+        <v>1</v>
+      </c>
+      <c r="G119" s="20" t="s">
         <v>457</v>
       </c>
-      <c r="H119" s="13" t="s">
+      <c r="H119" s="20" t="s">
         <v>526</v>
       </c>
-      <c r="I119" s="13" t="s">
+      <c r="I119" s="20" t="s">
         <v>527</v>
       </c>
-      <c r="J119" s="13">
-        <v>0</v>
-      </c>
-      <c r="K119" s="13">
-        <v>0</v>
-      </c>
-      <c r="L119" s="13">
-        <v>0</v>
-      </c>
-      <c r="M119" s="13">
-        <v>0</v>
-      </c>
-      <c r="N119" s="13">
-        <v>0</v>
-      </c>
-      <c r="O119" s="13">
-        <v>0</v>
-      </c>
-      <c r="P119" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q119" s="13" t="s">
+      <c r="J119" s="20">
+        <v>0</v>
+      </c>
+      <c r="K119" s="20">
+        <v>0</v>
+      </c>
+      <c r="L119" s="20">
+        <v>0</v>
+      </c>
+      <c r="M119" s="20">
+        <v>0</v>
+      </c>
+      <c r="N119" s="20">
+        <v>0</v>
+      </c>
+      <c r="O119" s="20">
+        <v>0</v>
+      </c>
+      <c r="P119" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q119" s="20" t="s">
         <v>528</v>
       </c>
-      <c r="R119">
+      <c r="R119" s="21">
         <v>3.0000000000000001E-62</v>
       </c>
-      <c r="S119" s="13">
+      <c r="S119" s="20">
         <v>0.99</v>
       </c>
-      <c r="T119" s="13" t="s">
+      <c r="T119" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="U119" s="13" t="s">
+      <c r="U119" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="V119" s="13" t="s">
+      <c r="V119" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="W119" s="13" t="s">
+      <c r="W119" s="20" t="s">
         <v>593</v>
       </c>
     </row>
@@ -12180,74 +12196,74 @@
         <v>592</v>
       </c>
     </row>
-    <row r="121" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A121" s="13" t="s">
+    <row r="121" spans="1:23" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A121" s="20" t="s">
         <v>278</v>
       </c>
-      <c r="B121" s="13" t="s">
+      <c r="B121" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="C121" s="13" t="s">
+      <c r="C121" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="D121" s="13">
+      <c r="D121" s="20">
         <v>0.115623</v>
       </c>
-      <c r="E121" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F121" s="13">
-        <v>1</v>
-      </c>
-      <c r="G121" s="13" t="s">
+      <c r="E121" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F121" s="20">
+        <v>1</v>
+      </c>
+      <c r="G121" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="H121" s="13" t="s">
+      <c r="H121" s="20" t="s">
         <v>279</v>
       </c>
-      <c r="I121" s="13" t="s">
+      <c r="I121" s="20" t="s">
         <v>280</v>
       </c>
-      <c r="J121" s="13">
-        <v>0</v>
-      </c>
-      <c r="K121" s="13">
-        <v>0</v>
-      </c>
-      <c r="L121" s="13">
-        <v>0</v>
-      </c>
-      <c r="M121" s="13">
-        <v>0</v>
-      </c>
-      <c r="N121" s="13">
-        <v>0</v>
-      </c>
-      <c r="O121" s="13">
-        <v>0</v>
-      </c>
-      <c r="P121" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q121" s="13" t="s">
+      <c r="J121" s="20">
+        <v>0</v>
+      </c>
+      <c r="K121" s="20">
+        <v>0</v>
+      </c>
+      <c r="L121" s="20">
+        <v>0</v>
+      </c>
+      <c r="M121" s="20">
+        <v>0</v>
+      </c>
+      <c r="N121" s="20">
+        <v>0</v>
+      </c>
+      <c r="O121" s="20">
+        <v>0</v>
+      </c>
+      <c r="P121" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q121" s="20" t="s">
         <v>281</v>
       </c>
-      <c r="R121">
+      <c r="R121" s="21">
         <v>6.0000000000000001E-64</v>
       </c>
-      <c r="S121" s="13">
-        <v>1</v>
-      </c>
-      <c r="T121" s="13" t="s">
+      <c r="S121" s="20">
+        <v>1</v>
+      </c>
+      <c r="T121" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="U121" s="13" t="s">
+      <c r="U121" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="V121" s="13" t="s">
+      <c r="V121" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="W121" s="13" t="s">
+      <c r="W121" s="20" t="s">
         <v>593</v>
       </c>
     </row>
@@ -12322,216 +12338,216 @@
         <v>592</v>
       </c>
     </row>
-    <row r="123" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A123" s="13" t="s">
+    <row r="123" spans="1:23" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="20" t="s">
         <v>417</v>
       </c>
-      <c r="B123" s="13" t="s">
+      <c r="B123" s="20" t="s">
         <v>359</v>
       </c>
-      <c r="C123" s="13" t="s">
+      <c r="C123" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="D123" s="13">
+      <c r="D123" s="20">
         <v>9.4195000000000001E-2</v>
       </c>
-      <c r="E123" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F123" s="13">
-        <v>1</v>
-      </c>
-      <c r="G123" s="13" t="s">
+      <c r="E123" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F123" s="20">
+        <v>1</v>
+      </c>
+      <c r="G123" s="20" t="s">
         <v>359</v>
       </c>
-      <c r="H123" s="13" t="s">
+      <c r="H123" s="20" t="s">
         <v>418</v>
       </c>
-      <c r="I123" s="13" t="s">
+      <c r="I123" s="20" t="s">
         <v>419</v>
       </c>
-      <c r="J123" s="13">
-        <v>0</v>
-      </c>
-      <c r="K123" s="13">
-        <v>1</v>
-      </c>
-      <c r="L123" s="13">
-        <v>0</v>
-      </c>
-      <c r="M123" s="13">
-        <v>1</v>
-      </c>
-      <c r="N123" s="13">
-        <v>0</v>
-      </c>
-      <c r="O123" s="13">
-        <v>1</v>
-      </c>
-      <c r="P123" s="13">
+      <c r="J123" s="20">
+        <v>0</v>
+      </c>
+      <c r="K123" s="20">
+        <v>1</v>
+      </c>
+      <c r="L123" s="20">
+        <v>0</v>
+      </c>
+      <c r="M123" s="20">
+        <v>1</v>
+      </c>
+      <c r="N123" s="20">
+        <v>0</v>
+      </c>
+      <c r="O123" s="20">
+        <v>1</v>
+      </c>
+      <c r="P123" s="20">
         <v>3</v>
       </c>
-      <c r="Q123" s="13" t="s">
+      <c r="Q123" s="20" t="s">
         <v>420</v>
       </c>
-      <c r="R123">
+      <c r="R123" s="21">
         <v>6.0000000000000001E-64</v>
       </c>
-      <c r="S123" s="13">
-        <v>1</v>
-      </c>
-      <c r="T123" s="13" t="s">
+      <c r="S123" s="20">
+        <v>1</v>
+      </c>
+      <c r="T123" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="U123" s="13" t="s">
+      <c r="U123" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="V123" s="13" t="s">
+      <c r="V123" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="W123" s="13" t="s">
+      <c r="W123" s="20" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="124" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A124" s="13" t="s">
+    <row r="124" spans="1:23" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="20" t="s">
         <v>306</v>
       </c>
-      <c r="B124" s="13" t="s">
+      <c r="B124" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="C124" s="13" t="s">
+      <c r="C124" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="D124" s="13">
+      <c r="D124" s="20">
         <v>9.9182999999999993E-2</v>
       </c>
-      <c r="E124" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F124" s="13">
-        <v>1</v>
-      </c>
-      <c r="G124" s="13" t="s">
+      <c r="E124" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F124" s="20">
+        <v>1</v>
+      </c>
+      <c r="G124" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="H124" s="13" t="s">
+      <c r="H124" s="20" t="s">
         <v>307</v>
       </c>
-      <c r="I124" s="13" t="s">
+      <c r="I124" s="20" t="s">
         <v>308</v>
       </c>
-      <c r="J124" s="13">
-        <v>0</v>
-      </c>
-      <c r="K124" s="13">
-        <v>0</v>
-      </c>
-      <c r="L124" s="13">
-        <v>0</v>
-      </c>
-      <c r="M124" s="13">
-        <v>0</v>
-      </c>
-      <c r="N124" s="13">
-        <v>0</v>
-      </c>
-      <c r="O124" s="13">
-        <v>0</v>
-      </c>
-      <c r="P124" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q124" s="13" t="s">
+      <c r="J124" s="20">
+        <v>0</v>
+      </c>
+      <c r="K124" s="20">
+        <v>0</v>
+      </c>
+      <c r="L124" s="20">
+        <v>0</v>
+      </c>
+      <c r="M124" s="20">
+        <v>0</v>
+      </c>
+      <c r="N124" s="20">
+        <v>0</v>
+      </c>
+      <c r="O124" s="20">
+        <v>0</v>
+      </c>
+      <c r="P124" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q124" s="20" t="s">
         <v>309</v>
       </c>
-      <c r="R124">
+      <c r="R124" s="21">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="S124" s="13">
+      <c r="S124" s="20">
         <v>0.8</v>
       </c>
-      <c r="T124" s="13" t="s">
+      <c r="T124" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="U124" s="13" t="s">
+      <c r="U124" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="V124" s="13" t="s">
+      <c r="V124" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="W124" s="13" t="s">
+      <c r="W124" s="20" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="125" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A125" s="13" t="s">
+    <row r="125" spans="1:23" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="B125" s="13" t="s">
+      <c r="B125" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="C125" s="13" t="s">
+      <c r="C125" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="D125" s="13">
+      <c r="D125" s="20">
         <v>0.105271</v>
       </c>
-      <c r="E125" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F125" s="13">
-        <v>1</v>
-      </c>
-      <c r="G125" s="13" t="s">
+      <c r="E125" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F125" s="20">
+        <v>1</v>
+      </c>
+      <c r="G125" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="H125" s="13" t="s">
+      <c r="H125" s="20" t="s">
         <v>206</v>
       </c>
-      <c r="I125" s="13" t="s">
+      <c r="I125" s="20" t="s">
         <v>207</v>
       </c>
-      <c r="J125" s="13">
-        <v>0</v>
-      </c>
-      <c r="K125" s="13">
-        <v>0</v>
-      </c>
-      <c r="L125" s="13">
-        <v>0</v>
-      </c>
-      <c r="M125" s="13">
-        <v>0</v>
-      </c>
-      <c r="N125" s="13">
-        <v>0</v>
-      </c>
-      <c r="O125" s="13">
-        <v>0</v>
-      </c>
-      <c r="P125" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q125" s="13" t="s">
+      <c r="J125" s="20">
+        <v>0</v>
+      </c>
+      <c r="K125" s="20">
+        <v>0</v>
+      </c>
+      <c r="L125" s="20">
+        <v>0</v>
+      </c>
+      <c r="M125" s="20">
+        <v>0</v>
+      </c>
+      <c r="N125" s="20">
+        <v>0</v>
+      </c>
+      <c r="O125" s="20">
+        <v>0</v>
+      </c>
+      <c r="P125" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q125" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="R125">
+      <c r="R125" s="21">
         <v>3.9999999999999999E-60</v>
       </c>
-      <c r="S125" s="13">
+      <c r="S125" s="20">
         <v>0.99</v>
       </c>
-      <c r="T125" s="13" t="s">
+      <c r="T125" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="U125" s="13" t="s">
+      <c r="U125" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="V125" s="13" t="s">
+      <c r="V125" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="W125" s="13" t="s">
+      <c r="W125" s="20" t="s">
         <v>593</v>
       </c>
     </row>

--- a/doc/Supplementary_2.xlsx
+++ b/doc/Supplementary_2.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nelly/bioinfo/Popgen_Qmacdougallii/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B795A9-A0AE-6249-878F-B613ED7A4E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FCE1B35-70AE-244A-A8AA-E36FFB84B88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16260" activeTab="3" xr2:uid="{BA0547B8-EBFB-8C4B-B87E-DC72CEAE7662}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16260" activeTab="2" xr2:uid="{BA0547B8-EBFB-8C4B-B87E-DC72CEAE7662}"/>
   </bookViews>
   <sheets>
     <sheet name="TS1" sheetId="2" r:id="rId1"/>
     <sheet name="TS2" sheetId="3" r:id="rId2"/>
     <sheet name="TS3" sheetId="7" r:id="rId3"/>
-    <sheet name="TS3_all_db" sheetId="5" r:id="rId4"/>
+    <sheet name="loc1050_pos159" sheetId="8" r:id="rId4"/>
+    <sheet name="TS3_all_db" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">TS3_all_db!$A$1:$A$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">TS3_all_db!$A$1:$A$125</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3483" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3489" uniqueCount="618">
   <si>
     <t>Code</t>
     <phoneticPr fontId="0" type="noConversion"/>
@@ -1881,6 +1882,24 @@
   </si>
   <si>
     <t>perc_identity_Magnoliopsida</t>
+  </si>
+  <si>
+    <t>Imagen</t>
+  </si>
+  <si>
+    <t>Pendiente. Imagen. En el alineamiento empieza en la pos95, lo que es después de la variante pos70</t>
+  </si>
+  <si>
+    <t>Pendiente. Imagen. Cae en una zona flanquante a la región traducida.</t>
+  </si>
+  <si>
+    <t>Pendiente. Imagen. Varios gaps aunque está en región codificante. Se podría hacer el ensamble con las lecturas crudas</t>
+  </si>
+  <si>
+    <t>Pendiente. Imagen. Gaps y la posición no se identificó bien - 122 0 126</t>
+  </si>
+  <si>
+    <t>Imagen. Sin cambio de aa</t>
   </si>
 </sst>
 </file>
@@ -3664,19 +3683,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B216AFF-E90D-6A40-B573-91B562BF736B}">
-  <dimension ref="A1:W125"/>
+  <dimension ref="A1:X125"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.6640625" customWidth="1"/>
     <col min="7" max="7" width="21.6640625" customWidth="1"/>
     <col min="8" max="8" width="23.1640625" customWidth="1"/>
-    <col min="9" max="9" width="21.6640625" customWidth="1"/>
+    <col min="9" max="9" width="145.1640625" customWidth="1"/>
     <col min="17" max="17" width="78.33203125" customWidth="1"/>
     <col min="18" max="18" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="18" t="s">
         <v>49</v>
       </c>
@@ -3747,7 +3766,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="2" spans="1:23" s="21" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="20" t="s">
         <v>547</v>
       </c>
@@ -3817,8 +3836,11 @@
       <c r="W2" s="20" t="s">
         <v>593</v>
       </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X2" s="21" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
         <v>300</v>
       </c>
@@ -3889,7 +3911,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
         <v>305</v>
       </c>
@@ -3960,7 +3982,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="5" spans="1:23" s="21" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="20" t="s">
         <v>573</v>
       </c>
@@ -4030,8 +4052,11 @@
       <c r="W5" s="20" t="s">
         <v>593</v>
       </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X5" s="21" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
         <v>432</v>
       </c>
@@ -4102,7 +4127,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
         <v>576</v>
       </c>
@@ -4173,7 +4198,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="13" t="s">
         <v>577</v>
       </c>
@@ -4244,7 +4269,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="13" t="s">
         <v>396</v>
       </c>
@@ -4315,7 +4340,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="13" t="s">
         <v>137</v>
       </c>
@@ -4386,7 +4411,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="11" spans="1:23" s="21" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="20" t="s">
         <v>505</v>
       </c>
@@ -4456,8 +4481,11 @@
       <c r="W11" s="20" t="s">
         <v>593</v>
       </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="21" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="13" t="s">
         <v>246</v>
       </c>
@@ -4528,7 +4556,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="13" t="s">
         <v>149</v>
       </c>
@@ -4599,7 +4627,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="13" t="s">
         <v>154</v>
       </c>
@@ -4670,7 +4698,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="13" t="s">
         <v>520</v>
       </c>
@@ -4741,7 +4769,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="16" spans="1:23" s="21" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="20" t="s">
         <v>542</v>
       </c>
@@ -4811,8 +4839,11 @@
       <c r="W16" s="20" t="s">
         <v>593</v>
       </c>
-    </row>
-    <row r="17" spans="1:23" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="X16" s="21" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="20" t="s">
         <v>378</v>
       </c>
@@ -4882,8 +4913,11 @@
       <c r="W17" s="20" t="s">
         <v>593</v>
       </c>
-    </row>
-    <row r="18" spans="1:23" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="X17" s="21" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="20" t="s">
         <v>107</v>
       </c>
@@ -4953,8 +4987,11 @@
       <c r="W18" s="20" t="s">
         <v>593</v>
       </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="21" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="13" t="s">
         <v>161</v>
       </c>
@@ -5025,7 +5062,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" s="13" t="s">
         <v>166</v>
       </c>
@@ -5096,7 +5133,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="13" t="s">
         <v>534</v>
       </c>
@@ -5167,7 +5204,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="13" t="s">
         <v>538</v>
       </c>
@@ -5238,7 +5275,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="13" t="s">
         <v>273</v>
       </c>
@@ -5309,7 +5346,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="13" t="s">
         <v>486</v>
       </c>
@@ -5380,7 +5417,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="13" t="s">
         <v>113</v>
       </c>
@@ -5451,7 +5488,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="13" t="s">
         <v>515</v>
       </c>
@@ -5522,7 +5559,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="13" t="s">
         <v>262</v>
       </c>
@@ -5593,78 +5630,78 @@
         <v>592</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A28" s="13" t="s">
+    <row r="28" spans="1:24" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="20" t="s">
         <v>457</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="D28" s="13">
+      <c r="D28" s="20">
         <v>0.19487199999999999</v>
       </c>
-      <c r="E28" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F28" s="13">
-        <v>1</v>
-      </c>
-      <c r="G28" s="13" t="s">
+      <c r="E28" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F28" s="20">
+        <v>1</v>
+      </c>
+      <c r="G28" s="20" t="s">
         <v>457</v>
       </c>
-      <c r="H28" s="13" t="s">
+      <c r="H28" s="20" t="s">
         <v>557</v>
       </c>
-      <c r="I28" s="13" t="s">
+      <c r="I28" s="20" t="s">
         <v>558</v>
       </c>
-      <c r="J28" s="13">
-        <v>0</v>
-      </c>
-      <c r="K28" s="13">
-        <v>0</v>
-      </c>
-      <c r="L28" s="13">
-        <v>0</v>
-      </c>
-      <c r="M28" s="13">
-        <v>0</v>
-      </c>
-      <c r="N28" s="13">
-        <v>0</v>
-      </c>
-      <c r="O28" s="13">
-        <v>0</v>
-      </c>
-      <c r="P28" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="13" t="s">
+      <c r="J28" s="20">
+        <v>0</v>
+      </c>
+      <c r="K28" s="20">
+        <v>0</v>
+      </c>
+      <c r="L28" s="20">
+        <v>0</v>
+      </c>
+      <c r="M28" s="20">
+        <v>0</v>
+      </c>
+      <c r="N28" s="20">
+        <v>0</v>
+      </c>
+      <c r="O28" s="20">
+        <v>0</v>
+      </c>
+      <c r="P28" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="20" t="s">
         <v>559</v>
       </c>
-      <c r="R28">
+      <c r="R28" s="21">
         <v>2.0000000000000001E-63</v>
       </c>
-      <c r="S28" s="13">
-        <v>1</v>
-      </c>
-      <c r="T28" s="13" t="s">
+      <c r="S28" s="20">
+        <v>1</v>
+      </c>
+      <c r="T28" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="U28" s="13" t="s">
+      <c r="U28" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="V28" s="13" t="s">
+      <c r="V28" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="W28" s="13" t="s">
+      <c r="W28" s="20" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="13" t="s">
         <v>565</v>
       </c>
@@ -5735,7 +5772,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="13" t="s">
         <v>171</v>
       </c>
@@ -5806,78 +5843,78 @@
         <v>592</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A31" s="13" t="s">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A31" s="20" t="s">
         <v>310</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="D31" s="13">
+      <c r="D31" s="20">
         <v>0.116813</v>
       </c>
-      <c r="E31" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F31" s="13">
+      <c r="E31" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F31" s="20">
         <v>2</v>
       </c>
-      <c r="G31" s="13" t="s">
+      <c r="G31" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="H31" s="13" t="s">
+      <c r="H31" s="20" t="s">
         <v>311</v>
       </c>
-      <c r="I31" s="13" t="s">
+      <c r="I31" s="20" t="s">
         <v>312</v>
       </c>
-      <c r="J31" s="13">
-        <v>0</v>
-      </c>
-      <c r="K31" s="13">
-        <v>0</v>
-      </c>
-      <c r="L31" s="13">
-        <v>0</v>
-      </c>
-      <c r="M31" s="13">
-        <v>1</v>
-      </c>
-      <c r="N31" s="13">
-        <v>0</v>
-      </c>
-      <c r="O31" s="13">
-        <v>0</v>
-      </c>
-      <c r="P31" s="13">
-        <v>1</v>
-      </c>
-      <c r="Q31" s="13" t="s">
+      <c r="J31" s="20">
+        <v>0</v>
+      </c>
+      <c r="K31" s="20">
+        <v>0</v>
+      </c>
+      <c r="L31" s="20">
+        <v>0</v>
+      </c>
+      <c r="M31" s="20">
+        <v>1</v>
+      </c>
+      <c r="N31" s="20">
+        <v>0</v>
+      </c>
+      <c r="O31" s="20">
+        <v>0</v>
+      </c>
+      <c r="P31" s="20">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="20" t="s">
         <v>313</v>
       </c>
-      <c r="R31">
+      <c r="R31" s="21">
         <v>8.0000000000000003E-56</v>
       </c>
-      <c r="S31" s="13">
-        <v>1</v>
-      </c>
-      <c r="T31" s="13" t="s">
+      <c r="S31" s="20">
+        <v>1</v>
+      </c>
+      <c r="T31" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="U31" s="13" t="s">
+      <c r="U31" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="V31" s="13" t="s">
+      <c r="V31" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="W31" s="13" t="s">
+      <c r="W31" s="20" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="13" t="s">
         <v>497</v>
       </c>
@@ -12567,6 +12604,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2978C0F-F0F4-AB42-87B1-21137AFE02B8}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9653607F-2617-9D48-9019-D0D5C5DB6416}">
   <dimension ref="A1:W125"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
